--- a/data/example/checkin/glycemic/human_chat_history.xlsx
+++ b/data/example/checkin/glycemic/human_chat_history.xlsx
@@ -474,14 +474,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>今天完成了25分钟快走和拉伸。</t>
+          <t>今天餐后散步22分钟，空腹血糖感觉比前几天稳定一些。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02 19:07</t>
+          <t>2026-03-02 12:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>@Quinn #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Quinn #daily_activity_checkin 做得不错，你这周的执行比较稳定。可以尝试把晚餐后活动固定下来，关注空腹和餐后血糖变化。</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>收到，我会继续按这个节奏控糖。</t>
         </is>
       </c>
     </row>
@@ -540,14 +540,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>今天完成了30分钟快走和拉伸。</t>
+          <t>上午快走后记录了血糖，下午又做了轻度力量训练。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-03 19:22</t>
+          <t>2026-03-03 13:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>@Riley #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Riley #daily_activity_checkin 今天反馈重点是控糖连续性。建议晚餐主食再略减一些，并保持饭后快走，你有明显进步。</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>好的，我明天把饭后步行时间再延长一点。</t>
         </is>
       </c>
     </row>
@@ -606,14 +606,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>今天完成了35分钟快走和拉伸。</t>
+          <t>今天控制了晚餐，总步数大概6150步，餐后活动也完成了。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-04 19:37</t>
+          <t>2026-03-04 11:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -628,14 +628,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>@Sofia #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Sofia #daily_activity_checkin 很棒，结合你目前的情况，推荐继续中等强度步行并记录空腹血糖，注意作息规律。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-04 19:40</t>
+          <t>2026-03-04 14:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>@Sofia #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Sofia #daily_activity_checkin 很好。根据你最近的血糖记录，建议餐后再步行10到15分钟，继续保持控糖节奏。</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>明白了，我会继续记录空腹和餐后情况。</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>今天完成了40分钟快走和拉伸。</t>
+          <t>今天按照计划运动，餐后没有吃零食，准备继续观察空腹血糖。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-05 19:55</t>
+          <t>2026-03-05 12:55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -716,14 +716,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>@Tessa #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Tessa #daily_activity_checkin 很好。根据你最近的血糖记录，建议餐后再步行10到15分钟，继续保持控糖节奏。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-05 19:58</t>
+          <t>2026-03-05 15:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>@Tessa #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Tessa #daily_activity_checkin 做得不错，你这周的执行比较稳定。可以尝试把晚餐后活动固定下来，关注空腹和餐后血糖变化。</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>收到，我会继续按这个节奏控糖。</t>
         </is>
       </c>
     </row>
@@ -782,14 +782,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>今天完成了45分钟快走和拉伸。</t>
+          <t>今天餐后散步38分钟，空腹血糖感觉比前几天稳定一些。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06 19:13</t>
+          <t>2026-03-06 13:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>@Uma #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Uma #daily_activity_checkin 做得不错，你这周的执行比较稳定。可以尝试把晚餐后活动固定下来，关注空腹和餐后血糖变化。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-06 19:16</t>
+          <t>2026-03-06 16:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>@Uma #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Uma #daily_activity_checkin 今天反馈重点是控糖连续性。建议晚餐主食再略减一些，并保持饭后快走，你有明显进步。</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>好的，我明天把饭后步行时间再延长一点。</t>
         </is>
       </c>
     </row>
@@ -870,14 +870,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>今天完成了50分钟快走和拉伸。</t>
+          <t>上午快走后记录了血糖，下午又做了轻度力量训练。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-07 19:31</t>
+          <t>2026-03-07 11:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -892,14 +892,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>@Vera #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Vera #daily_activity_checkin 今天反馈重点是控糖连续性。建议晚餐主食再略减一些，并保持饭后快走，你有明显进步。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-07 19:34</t>
+          <t>2026-03-07 14:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -914,14 +914,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>@Vera #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Vera #daily_activity_checkin 很棒，结合你目前的情况，推荐继续中等强度步行并记录空腹血糖，注意作息规律。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-07 19:37</t>
+          <t>2026-03-07 17:37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>@Vera #daily_activity_checkin 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Vera #daily_activity_checkin 很好。根据你最近的血糖记录，建议餐后再步行10到15分钟，继续保持控糖节奏。</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>明白了，我会继续记录空腹和餐后情况。</t>
         </is>
       </c>
     </row>
@@ -980,14 +980,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>今天完成了55分钟快走和拉伸。</t>
+          <t>今天控制了晚餐，总步数大概8750步，餐后活动也完成了。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-08 19:52</t>
+          <t>2026-03-08 12:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>@Wendy #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Wendy #daily_activity_checkin 很棒，结合你目前的情况，推荐继续中等强度步行并记录空腹血糖，注意作息规律。</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>收到，我会继续按这个节奏控糖。</t>
         </is>
       </c>
     </row>
@@ -1046,14 +1046,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>今天完成了60分钟快走和拉伸。</t>
+          <t>今天按照计划运动，餐后没有吃零食，准备继续观察空腹血糖。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09 19:07</t>
+          <t>2026-03-09 13:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>@Xena #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Xena #daily_activity_checkin 很好。根据你最近的血糖记录，建议餐后再步行10到15分钟，继续保持控糖节奏。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09 19:10</t>
+          <t>2026-03-09 16:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>@Xena #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Xena #daily_activity_checkin 做得不错，你这周的执行比较稳定。可以尝试把晚餐后活动固定下来，关注空腹和餐后血糖变化。</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>好的，我明天把饭后步行时间再延长一点。</t>
         </is>
       </c>
     </row>
